--- a/documents/batch-disbursement/test-cases/valid-data.xlsx
+++ b/documents/batch-disbursement/test-cases/valid-data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
   <si>
     <t xml:space="preserve">STT</t>
   </si>
@@ -64,13 +64,13 @@
     <t xml:space="preserve">0120508601T45001-33218196</t>
   </si>
   <si>
-    <t xml:space="preserve">DUONG DUY MEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">886274030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">056201010052</t>
+    <t xml:space="preserve">LE TUAN ANH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">977517399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">091095010579</t>
   </si>
   <si>
     <t xml:space="preserve">36000000</t>
@@ -88,15 +88,43 @@
     <t xml:space="preserve">0120508601T45001-33218555</t>
   </si>
   <si>
+    <t xml:space="preserve">TRAN NHU BACH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">886277119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">001088010672</t>
+  </si>
+  <si>
     <t xml:space="preserve">Giai ngan hop dong 0120508601T45001-33218555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0120508601T46109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0120508601T45001-33218914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGO THI KIM THINH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">933344567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">079191007008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giai ngan hop dong 0120508601T45001-33218914</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -173,7 +201,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -366,8 +394,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K1048576"/>
+  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="28.61"/>
@@ -463,13 +491,13 @@
         <v>21</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>17</v>
@@ -481,9 +509,156 @@
         <v>18</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
